--- a/individual_Tests/klee_posix_findings.xlsx
+++ b/individual_Tests/klee_posix_findings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jorge\Desktop\Masters\Tests\initial_tests\individual_Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6ABEDB9-EE0D-4423-8B20-297E908CBEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA187CA-05B4-4CF6-A2B0-ECB4264FD5C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="127">
   <si>
     <t>Bug ID</t>
   </si>
@@ -402,6 +402,9 @@
   </si>
   <si>
     <t>NEED TO DOUBLE CHECK CONSEQUENCES OF THIS FLAG. ALSO SINCE MOST OF THESE FLAGS ARE NOT IMPLEMENTED IS IT BAD TO DISCARD?</t>
+  </si>
+  <si>
+    <t>st_mode = (st_mode &amp; ~0777) | (0644 &amp; ~__exe_env.umask)</t>
   </si>
 </sst>
 </file>
@@ -545,7 +548,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -582,6 +585,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -903,7 +909,7 @@
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="56" customWidth="1"/>
-    <col min="9" max="9" width="27.85546875" customWidth="1"/>
+    <col min="9" max="9" width="61.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1061,6 +1067,9 @@
       <c r="H6" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="I6" s="17" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -1331,7 +1340,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
@@ -1355,6 +1364,9 @@
       </c>
       <c r="H17" s="5" t="s">
         <v>110</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
